--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(3).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="494">
   <si>
     <t>ID</t>
   </si>
@@ -87,6 +87,9 @@
     <t>只听“哐当”一声脆响，镜面瞬间裂成蛛网般的碎片，沾着水汽的玻璃顺着力道在暗室的地面上溅射出一道亮晶晶的扇形轨迹。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
@@ -121,6 +124,9 @@
   </si>
   <si>
     <t>克拉克伸手抹了把溅在袖口上的玻璃渣，手中的光圈往四面一扫。无数核桃状的大脑瞬间犹如漫天的炮弹般轰入你们的眼帘，它们或是被泡在标注着编号的透明标本瓶里，或是被打上蜡封陈列在两侧的铁架上。</t>
+  </si>
+  <si>
+    <t>16 enhanced_suspence</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=3</t>
@@ -302,6 +308,9 @@
   </si>
   <si>
     <t>“......研究表明，人类在快速眼动睡眠期间，大脑前额叶皮层的活跃度显著降低，而杏仁核与海马体的连接则趋于增强。这解释了为何梦境内容往往带有强烈的情感色彩，却缺乏逻辑连贯性.......”</t>
+  </si>
+  <si>
+    <t>11 enhanced the_mountain-hope-background</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=20</t>
@@ -721,6 +730,9 @@
   </si>
   <si>
     <t>克拉克的身体猛地一震，每一寸因疲惫而松弛的肌肉都在这百分之一秒的惊诧间被瞬间唤醒。</t>
+  </si>
+  <si>
+    <t>5 enhanced leberch-suspense</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=51</t>
@@ -2865,21 +2877,21 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="40.5" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -2897,7 +2909,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -2909,15 +2921,15 @@
         <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" ht="55.5" spans="1:12">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2935,7 +2947,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2950,12 +2962,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="67.5" spans="1:12">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2973,13 +2985,13 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -2988,12 +3000,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -3011,7 +3023,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -3026,7 +3038,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="55.5" spans="1:12">
@@ -3049,7 +3061,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3061,24 +3073,24 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -3087,7 +3099,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3099,15 +3111,15 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:12">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3116,7 +3128,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -3125,7 +3137,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3137,15 +3149,15 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" ht="57" spans="1:12">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -3163,7 +3175,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3178,15 +3190,15 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:12">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -3201,7 +3213,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3216,15 +3228,15 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:12">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -3239,7 +3251,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3254,12 +3266,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" ht="40.5" spans="1:12">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3277,7 +3289,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3292,12 +3304,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:12">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3315,7 +3327,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3327,15 +3339,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:12">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3353,7 +3365,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3368,12 +3380,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="45" spans="1:12">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3391,7 +3403,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3406,12 +3418,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" ht="69" spans="1:12">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3429,7 +3441,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3444,12 +3456,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" ht="70.5" spans="1:12">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3467,7 +3479,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3482,12 +3494,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:12">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3505,7 +3517,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3520,12 +3532,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3543,7 +3555,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3555,15 +3567,15 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="28.5" spans="1:12">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3581,27 +3593,27 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J21" t="s">
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" ht="57" spans="1:12">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3619,13 +3631,13 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
@@ -3634,12 +3646,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" ht="27" spans="1:12">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3657,7 +3669,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3672,12 +3684,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3695,7 +3707,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3710,12 +3722,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" ht="45" spans="1:12">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3733,7 +3745,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3748,12 +3760,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3771,7 +3783,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3786,21 +3798,21 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3809,7 +3821,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3821,15 +3833,15 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3838,7 +3850,7 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3847,7 +3859,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3859,15 +3871,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" ht="55.5" spans="1:12">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3885,7 +3897,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3900,12 +3912,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" ht="42" spans="1:12">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3923,7 +3935,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3938,12 +3950,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" ht="40.5" spans="1:12">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3961,7 +3973,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3976,15 +3988,15 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" ht="72" spans="1:12">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -3999,7 +4011,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4014,15 +4026,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" ht="42" spans="1:12">
       <c r="A33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -4037,7 +4049,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4052,12 +4064,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" ht="67.5" spans="1:12">
       <c r="A34" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4075,7 +4087,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4090,12 +4102,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4128,27 +4140,27 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" ht="90" spans="1:12">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F36" t="s">
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4160,15 +4172,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" ht="54" spans="1:12">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4177,7 +4189,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4186,7 +4198,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4198,15 +4210,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L37" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4224,7 +4236,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4239,21 +4251,21 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" ht="54" spans="1:12">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4262,7 +4274,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4274,15 +4286,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L39" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" ht="42" spans="1:12">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4291,7 +4303,7 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4300,7 +4312,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4312,18 +4324,18 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L40" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4338,7 +4350,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4353,12 +4365,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" ht="40.5" spans="1:12">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4376,7 +4388,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4391,15 +4403,15 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
@@ -4414,7 +4426,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4429,15 +4441,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4452,7 +4464,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4467,12 +4479,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" ht="54" spans="1:12">
       <c r="A45" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4490,7 +4502,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4505,15 +4517,15 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" ht="28.5" spans="1:12">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -4528,7 +4540,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4543,15 +4555,15 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -4566,7 +4578,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4581,12 +4593,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4619,12 +4631,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" ht="90" spans="1:12">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4642,7 +4654,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4657,12 +4669,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" ht="40.5" spans="1:12">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4680,7 +4692,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4695,15 +4707,15 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -4718,7 +4730,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4733,12 +4745,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4756,7 +4768,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4771,12 +4783,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4794,7 +4806,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4806,18 +4818,18 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="L53" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B54" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
@@ -4832,7 +4844,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4847,12 +4859,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" ht="42" spans="1:12">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4870,7 +4882,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4885,15 +4897,15 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" ht="28.5" spans="1:12">
       <c r="A56" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -4908,7 +4920,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4923,15 +4935,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" ht="42" spans="1:12">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4946,7 +4958,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4961,12 +4973,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" ht="40.5" spans="1:12">
       <c r="A58" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4984,7 +4996,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4999,12 +5011,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" ht="42" spans="1:12">
       <c r="A59" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5022,7 +5034,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5037,12 +5049,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" ht="40.5" spans="1:12">
       <c r="A60" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5060,7 +5072,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5075,12 +5087,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5098,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5110,18 +5122,18 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L61" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -5136,24 +5148,24 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J62" t="s">
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="63" ht="27" spans="1:12">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5171,13 +5183,13 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>15</v>
+        <v>215</v>
       </c>
       <c r="J63" t="s">
         <v>15</v>
@@ -5186,12 +5198,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5209,7 +5221,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5221,15 +5233,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L64" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" ht="27" spans="1:12">
       <c r="A65" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5247,7 +5259,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5262,12 +5274,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" ht="45" spans="1:12">
       <c r="A66" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5297,15 +5309,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L66" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5338,12 +5350,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" ht="42" spans="1:12">
       <c r="A68" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5361,7 +5373,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5376,12 +5388,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69" ht="55.5" spans="1:12">
       <c r="A69" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5399,7 +5411,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5414,12 +5426,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" ht="72" spans="1:12">
       <c r="A70" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5437,7 +5449,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5449,15 +5461,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="L70" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5475,7 +5487,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5490,12 +5502,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" ht="57" spans="1:12">
       <c r="A72" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5513,7 +5525,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5528,12 +5540,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" ht="43.5" spans="1:12">
       <c r="A73" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5551,7 +5563,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5566,12 +5578,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" ht="72" spans="1:12">
       <c r="A74" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5589,7 +5601,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5604,12 +5616,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5627,7 +5639,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5642,12 +5654,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="76" ht="40.5" spans="1:12">
       <c r="A76" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5665,7 +5677,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5680,12 +5692,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" ht="55.5" spans="1:12">
       <c r="A77" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5703,7 +5715,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5715,12 +5727,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5738,7 +5750,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5750,18 +5762,18 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="L78" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B79" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -5776,7 +5788,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5791,12 +5803,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" ht="27" spans="1:12">
       <c r="A80" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5814,7 +5826,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5826,18 +5838,18 @@
         <v>15</v>
       </c>
       <c r="K80" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L80" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B81" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -5852,7 +5864,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5867,12 +5879,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="82" ht="27" spans="1:12">
       <c r="A82" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5890,7 +5902,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5902,15 +5914,15 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5943,12 +5955,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" ht="42" spans="1:12">
       <c r="A84" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5966,7 +5978,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5981,12 +5993,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85" ht="43.5" spans="1:12">
       <c r="A85" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6004,7 +6016,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6019,12 +6031,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6042,7 +6054,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6057,12 +6069,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" ht="54" spans="1:12">
       <c r="A87" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6080,7 +6092,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6092,15 +6104,15 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="L87" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="88" ht="54" spans="1:12">
       <c r="A88" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6118,7 +6130,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6133,12 +6145,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" ht="40.5" spans="1:12">
       <c r="A89" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6156,7 +6168,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6171,12 +6183,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6194,7 +6206,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6209,12 +6221,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6232,7 +6244,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6247,12 +6259,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92" ht="54" spans="1:12">
       <c r="A92" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6270,7 +6282,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6282,18 +6294,18 @@
         <v>15</v>
       </c>
       <c r="K92" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="L92" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B93" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
@@ -6308,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6323,12 +6335,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="94" ht="55.5" spans="1:12">
       <c r="A94" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6346,7 +6358,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6361,12 +6373,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="95" ht="55.5" spans="1:12">
       <c r="A95" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6384,7 +6396,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6396,15 +6408,15 @@
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L95" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="96" ht="40.5" spans="1:12">
       <c r="A96" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6422,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6437,15 +6449,15 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B97" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -6460,7 +6472,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6475,12 +6487,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" ht="42" spans="1:12">
       <c r="A98" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6498,7 +6510,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6513,12 +6525,12 @@
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="99" ht="55.5" spans="1:12">
       <c r="A99" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6536,7 +6548,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6548,10 +6560,10 @@
         <v>15</v>
       </c>
       <c r="K99" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="L99" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -6572,39 +6584,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6612,15 +6624,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6628,66 +6640,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B13" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B14" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B15" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -6709,616 +6721,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E5" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B6" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C6" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D6" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E6" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B7" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C7" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D7" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E7" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B8" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C8" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D8" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E8" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F8" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B9" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C9" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D9" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E9" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F9" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B10" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C10" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D10" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E10" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F10" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B11" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C11" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D11" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E11" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F11" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B12" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C12" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D12" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E12" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F12" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B13" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C13" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D13" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E13" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F13" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B14" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C14" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D14" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E14" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F14" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B15" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C15" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D15" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E15" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F15" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B16" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C16" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D16" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E16" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F16" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B17" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C17" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D17" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E17" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F17" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B18" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C18" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D18" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E18" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F18" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B19" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C19" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D19" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E19" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F19" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B20" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C20" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D20" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E20" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F20" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B21" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C21" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D21" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E21" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F21" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B22" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C22" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D22" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E22" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F22" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B23" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C23" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D23" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E23" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="F23" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B24" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C24" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D24" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E24" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F24" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B25" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C25" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D25" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E25" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F25" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B26" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C26" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D26" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E26" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F26" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B27" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C27" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D27" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E27" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F27" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B28" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C28" t="s">
+        <v>477</v>
+      </c>
+      <c r="D28" t="s">
         <v>473</v>
       </c>
-      <c r="D28" t="s">
-        <v>469</v>
-      </c>
       <c r="E28" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F28" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B29" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C29" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D29" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E29" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F29" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B30" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C30" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D30" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E30" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F30" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B31" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C31" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D31" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线3层（中下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="498">
   <si>
     <t>ID</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>16 enhanced_suspence</t>
+  </si>
+  <si>
+    <t>unlockscene(scene1)&amp;unlockmusic(Music16)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=3</t>
@@ -311,6 +314,9 @@
   </si>
   <si>
     <t>11 enhanced the_mountain-hope-background</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music11)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=20</t>
@@ -735,6 +741,9 @@
     <t>5 enhanced leberch-suspense</t>
   </si>
   <si>
+    <t>unlockmusic(Music5)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=51</t>
   </si>
   <si>
@@ -854,6 +863,9 @@
   </si>
   <si>
     <t>信件以一个神秘的落款结束，没有留下更多的身份信息，但这段全篇充满了谎言与威胁意味的文字却像浸了毒的蜜糖，黏在你的思绪中久久难以忘怀。</t>
+  </si>
+  <si>
+    <t>unlockscene(scene2)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=64</t>
@@ -2997,15 +3009,15 @@
         <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="40.5" spans="1:12">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -3023,7 +3035,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -3038,7 +3050,7 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="55.5" spans="1:12">
@@ -3061,7 +3073,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3073,24 +3085,24 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -3099,7 +3111,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3111,15 +3123,15 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:12">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3128,7 +3140,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -3137,7 +3149,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3149,15 +3161,15 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="57" spans="1:12">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -3175,7 +3187,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3190,15 +3202,15 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:12">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -3213,7 +3225,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3228,15 +3240,15 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -3251,7 +3263,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3266,12 +3278,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="40.5" spans="1:12">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3289,7 +3301,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3304,12 +3316,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="30" spans="1:12">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3327,7 +3339,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3339,15 +3351,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:12">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3365,7 +3377,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3380,12 +3392,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="45" spans="1:12">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3403,7 +3415,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3418,12 +3430,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" ht="69" spans="1:12">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3441,7 +3453,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3456,12 +3468,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" ht="70.5" spans="1:12">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3479,7 +3491,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3494,12 +3506,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:12">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3517,7 +3529,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3532,12 +3544,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3555,7 +3567,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3567,15 +3579,15 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="28.5" spans="1:12">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3593,7 +3605,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3605,15 +3617,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" ht="57" spans="1:12">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3631,27 +3643,27 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="L22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" ht="27" spans="1:12">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3669,7 +3681,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3684,12 +3696,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3707,7 +3719,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3722,12 +3734,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" ht="45" spans="1:12">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3745,7 +3757,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3760,12 +3772,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" ht="54" spans="1:12">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3783,7 +3795,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3798,21 +3810,21 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3821,7 +3833,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3833,15 +3845,15 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3850,7 +3862,7 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3859,7 +3871,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3871,15 +3883,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" ht="55.5" spans="1:12">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3897,7 +3909,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3912,12 +3924,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" ht="42" spans="1:12">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3935,7 +3947,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3950,12 +3962,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" ht="40.5" spans="1:12">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3973,7 +3985,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3988,15 +4000,15 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" ht="72" spans="1:12">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -4011,7 +4023,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4026,15 +4038,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" ht="42" spans="1:12">
       <c r="A33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -4049,7 +4061,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4064,12 +4076,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" ht="67.5" spans="1:12">
       <c r="A34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4087,7 +4099,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4102,12 +4114,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4140,27 +4152,27 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" ht="90" spans="1:12">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F36" t="s">
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4172,15 +4184,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" ht="54" spans="1:12">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4189,7 +4201,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4198,7 +4210,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4210,15 +4222,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L37" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4236,7 +4248,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4251,21 +4263,21 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" ht="54" spans="1:12">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4274,7 +4286,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4286,15 +4298,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L39" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" ht="42" spans="1:12">
       <c r="A40" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4303,7 +4315,7 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4312,7 +4324,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4324,18 +4336,18 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L40" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4350,7 +4362,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4365,12 +4377,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" ht="40.5" spans="1:12">
       <c r="A42" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4388,7 +4400,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4403,15 +4415,15 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B43" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
@@ -4426,7 +4438,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4441,15 +4453,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4464,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4479,12 +4491,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" ht="54" spans="1:12">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4502,7 +4514,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4517,15 +4529,15 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" ht="28.5" spans="1:12">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -4540,7 +4552,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4555,15 +4567,15 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -4578,7 +4590,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4593,12 +4605,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4631,12 +4643,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" ht="90" spans="1:12">
       <c r="A49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4654,7 +4666,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4669,12 +4681,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" ht="40.5" spans="1:12">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4692,7 +4704,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4707,15 +4719,15 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -4730,7 +4742,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4745,12 +4757,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4768,7 +4780,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4783,12 +4795,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" ht="40.5" spans="1:12">
       <c r="A53" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4806,7 +4818,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4818,18 +4830,18 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L53" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
@@ -4844,7 +4856,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4859,12 +4871,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" ht="42" spans="1:12">
       <c r="A55" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4882,7 +4894,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4897,15 +4909,15 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="56" ht="28.5" spans="1:12">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -4920,7 +4932,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4935,15 +4947,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="57" ht="42" spans="1:12">
       <c r="A57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4958,7 +4970,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4973,12 +4985,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" ht="40.5" spans="1:12">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4996,7 +5008,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5011,12 +5023,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" ht="42" spans="1:12">
       <c r="A59" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5034,7 +5046,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5049,12 +5061,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" ht="40.5" spans="1:12">
       <c r="A60" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5072,7 +5084,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5087,12 +5099,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5110,7 +5122,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5122,18 +5134,18 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L61" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B62" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -5148,7 +5160,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5160,12 +5172,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5183,27 +5195,27 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J63" t="s">
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>15</v>
+        <v>218</v>
       </c>
       <c r="L63" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5221,7 +5233,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5233,15 +5245,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L64" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" ht="27" spans="1:12">
       <c r="A65" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5259,7 +5271,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5274,12 +5286,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" ht="45" spans="1:12">
       <c r="A66" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5309,15 +5321,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L66" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5350,12 +5362,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" ht="42" spans="1:12">
       <c r="A68" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5373,7 +5385,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5388,12 +5400,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" ht="55.5" spans="1:12">
       <c r="A69" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5411,7 +5423,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5426,12 +5438,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="70" ht="72" spans="1:12">
       <c r="A70" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5449,7 +5461,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5461,15 +5473,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L70" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" ht="40.5" spans="1:12">
       <c r="A71" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5487,7 +5499,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5502,12 +5514,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" ht="57" spans="1:12">
       <c r="A72" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5525,7 +5537,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5540,12 +5552,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="73" ht="43.5" spans="1:12">
       <c r="A73" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5563,7 +5575,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5578,12 +5590,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" ht="72" spans="1:12">
       <c r="A74" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5601,7 +5613,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5616,12 +5628,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5639,7 +5651,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5654,12 +5666,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" ht="40.5" spans="1:12">
       <c r="A76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5677,7 +5689,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5689,15 +5701,15 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="L76" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" ht="55.5" spans="1:12">
       <c r="A77" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5715,7 +5727,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5727,12 +5739,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5750,7 +5762,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5762,18 +5774,18 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="L78" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B79" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
@@ -5788,7 +5800,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5803,12 +5815,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" ht="27" spans="1:12">
       <c r="A80" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5826,7 +5838,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5838,18 +5850,18 @@
         <v>15</v>
       </c>
       <c r="K80" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="L80" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B81" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -5864,7 +5876,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5879,12 +5891,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" ht="27" spans="1:12">
       <c r="A82" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5902,7 +5914,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5914,15 +5926,15 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5955,12 +5967,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="84" ht="42" spans="1:12">
       <c r="A84" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5978,7 +5990,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5993,12 +6005,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" ht="43.5" spans="1:12">
       <c r="A85" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6016,7 +6028,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6031,12 +6043,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6054,7 +6066,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6069,12 +6081,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="87" ht="54" spans="1:12">
       <c r="A87" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6092,7 +6104,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6104,15 +6116,15 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="L87" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" ht="54" spans="1:12">
       <c r="A88" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6130,7 +6142,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6145,12 +6157,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89" ht="40.5" spans="1:12">
       <c r="A89" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6168,7 +6180,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6183,12 +6195,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="90" ht="54" spans="1:12">
       <c r="A90" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6206,7 +6218,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6221,12 +6233,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6244,7 +6256,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6259,12 +6271,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" ht="54" spans="1:12">
       <c r="A92" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6282,7 +6294,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6294,18 +6306,18 @@
         <v>15</v>
       </c>
       <c r="K92" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L92" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B93" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
@@ -6320,7 +6332,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6335,12 +6347,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="94" ht="55.5" spans="1:12">
       <c r="A94" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6358,7 +6370,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6373,12 +6385,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="95" ht="55.5" spans="1:12">
       <c r="A95" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6396,7 +6408,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6408,15 +6420,15 @@
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L95" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="96" ht="40.5" spans="1:12">
       <c r="A96" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6434,7 +6446,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6449,15 +6461,15 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B97" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -6472,7 +6484,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6487,12 +6499,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="98" ht="42" spans="1:12">
       <c r="A98" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6510,7 +6522,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6525,12 +6537,12 @@
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="99" ht="55.5" spans="1:12">
       <c r="A99" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6548,7 +6560,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6560,10 +6572,10 @@
         <v>15</v>
       </c>
       <c r="K99" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="L99" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -6584,39 +6596,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6624,7 +6636,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -6632,7 +6644,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -6640,66 +6652,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B10" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B11" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B12" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B13" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -6721,616 +6733,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C5" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E5" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F6" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C7" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D7" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E7" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F7" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B8" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C8" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D8" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E8" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F8" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B9" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C9" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D9" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E9" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F9" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B10" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C10" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D10" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E10" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F10" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B11" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C11" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D11" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E11" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F11" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B12" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C12" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D12" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E12" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F12" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B13" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C13" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D13" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E13" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F13" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B14" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C14" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D14" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E14" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F14" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B15" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D15" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E15" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F15" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B16" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C16" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D16" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E16" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F16" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B17" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C17" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D17" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E17" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F17" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B18" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C18" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D18" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E18" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F18" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B19" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C19" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D19" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E19" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F19" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B20" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C20" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D20" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E20" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F20" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B21" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C21" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D21" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E21" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F21" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B22" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C22" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D22" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E22" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F22" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B23" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C23" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D23" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E23" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F23" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B24" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C24" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D24" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E24" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F24" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B25" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C25" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D25" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E25" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="F25" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B26" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C26" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D26" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E26" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="F26" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B27" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C27" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D27" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E27" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F27" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B28" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C28" t="s">
+        <v>481</v>
+      </c>
+      <c r="D28" t="s">
         <v>477</v>
       </c>
-      <c r="D28" t="s">
-        <v>473</v>
-      </c>
       <c r="E28" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F28" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B29" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C29" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D29" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E29" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F29" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B30" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C30" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D30" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E30" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F30" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B31" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C31" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D31" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
